--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T09:40:37+00:00</t>
+    <t>2024-11-07T06:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T06:21:30+00:00</t>
+    <t>2024-11-07T13:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T13:12:32+00:00</t>
+    <t>2024-11-07T14:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T14:31:26+00:00</t>
+    <t>2024-11-08T06:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:16:09+00:00</t>
+    <t>2024-11-12T07:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,10 +451,10 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>CoverageEligibilityRequest.extension:verlängerungstage</t>
-  </si>
-  <si>
-    <t>verlängerungstage</t>
+    <t>CoverageEligibilityRequest.extension:verlaengerungstage</t>
+  </si>
+  <si>
+    <t>verlaengerungstage</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verlaengerungstage}
@@ -477,10 +477,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">"KLAS – Allgemeine Gebührenklasse/Sonderklasse" </t>
-  </si>
-  <si>
-    <t>"KLAS – Allgemeine Gebührenklasse/Sonderklasse"</t>
+    <t>KLAS: Allgemeine Gebuehrenklasse bzw. Sonderklasse</t>
   </si>
   <si>
     <t>CoverageEligibilityRequest.modifierExtension</t>
@@ -962,7 +959,7 @@
     <t>CoverageEligibilityRequest.insurance.coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/SVCCoverage)
+    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MOPEDCoverage)
 </t>
   </si>
   <si>
@@ -1491,7 +1488,7 @@
   <cols>
     <col min="1" max="1" width="56.875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="56.875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.4296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2706,7 +2703,7 @@
         <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2786,14 +2783,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2815,16 +2812,16 @@
         <v>133</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -2873,7 +2870,7 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2902,10 +2899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2928,17 +2925,17 @@
         <v>19</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>19</v>
@@ -2987,7 +2984,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3002,10 +2999,10 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>19</v>
@@ -3016,10 +3013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3045,16 +3042,16 @@
         <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -3082,11 +3079,11 @@
         <v>110</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3103,7 +3100,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>86</v>
@@ -3118,10 +3115,10 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>19</v>
@@ -3132,10 +3129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3158,17 +3155,17 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3193,14 +3190,14 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
       </c>
@@ -3217,7 +3214,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3232,10 +3229,10 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>19</v>
@@ -3246,10 +3243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3275,14 +3272,14 @@
         <v>106</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3310,11 +3307,11 @@
         <v>110</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
       </c>
@@ -3331,7 +3328,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>86</v>
@@ -3349,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>19</v>
@@ -3360,10 +3357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3386,19 +3383,19 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -3447,7 +3444,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>86</v>
@@ -3462,10 +3459,10 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>19</v>
@@ -3476,10 +3473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3502,13 +3499,13 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3559,7 +3556,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3588,10 +3585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3614,13 +3611,13 @@
         <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3671,43 +3668,43 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI19" t="s" s="2">
+      <c r="AJ19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3729,13 +3726,13 @@
         <v>133</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="N20" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3785,7 +3782,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3809,19 +3806,19 @@
         <v>19</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3843,16 +3840,16 @@
         <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="N21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -3901,7 +3898,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3930,10 +3927,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3956,13 +3953,13 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3989,11 +3986,11 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -4011,7 +4008,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>86</v>
@@ -4040,10 +4037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4066,13 +4063,13 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4123,7 +4120,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -4152,10 +4149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4178,17 +4175,17 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4237,7 +4234,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4255,7 +4252,7 @@
         <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>19</v>
@@ -4266,10 +4263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4292,17 +4289,17 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -4351,7 +4348,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>86</v>
@@ -4366,10 +4363,10 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>19</v>
@@ -4380,10 +4377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4406,17 +4403,17 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -4465,7 +4462,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4483,7 +4480,7 @@
         <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>19</v>
@@ -4494,10 +4491,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4520,19 +4517,19 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -4581,7 +4578,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4596,10 +4593,10 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
@@ -4610,10 +4607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4636,17 +4633,17 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -4695,7 +4692,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>86</v>
@@ -4710,10 +4707,10 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>19</v>
@@ -4724,10 +4721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4750,17 +4747,17 @@
         <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -4809,7 +4806,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4827,7 +4824,7 @@
         <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>19</v>
@@ -4838,10 +4835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4864,19 +4861,19 @@
         <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -4925,7 +4922,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4954,10 +4951,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4980,13 +4977,13 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5037,43 +5034,43 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI31" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI31" t="s" s="2">
+      <c r="AJ31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5095,13 +5092,13 @@
         <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="N32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5151,7 +5148,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5175,19 +5172,19 @@
         <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5209,16 +5206,16 @@
         <v>133</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="N33" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5267,7 +5264,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5296,10 +5293,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5322,17 +5319,17 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -5381,7 +5378,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>86</v>
@@ -5410,10 +5407,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5436,19 +5433,19 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -5497,7 +5494,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>86</v>
@@ -5526,10 +5523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5552,17 +5549,17 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -5611,7 +5608,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5640,10 +5637,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5666,19 +5663,19 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -5727,7 +5724,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5756,10 +5753,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5782,13 +5779,13 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5839,43 +5836,43 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI38" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI38" t="s" s="2">
+      <c r="AJ38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5897,13 +5894,13 @@
         <v>133</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="N39" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5953,7 +5950,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5977,19 +5974,19 @@
         <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6011,16 +6008,16 @@
         <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="N40" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -6069,7 +6066,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6098,10 +6095,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6124,19 +6121,19 @@
         <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6185,7 +6182,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6214,10 +6211,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6240,17 +6237,17 @@
         <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6299,7 +6296,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>86</v>
@@ -6328,10 +6325,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6354,17 +6351,17 @@
         <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -6413,7 +6410,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6442,10 +6439,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6468,17 +6465,17 @@
         <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
@@ -6527,7 +6524,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6556,10 +6553,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6582,13 +6579,13 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6639,43 +6636,43 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI45" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI45" t="s" s="2">
+      <c r="AJ45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6697,13 +6694,13 @@
         <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="N46" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6753,7 +6750,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6777,19 +6774,19 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6811,16 +6808,16 @@
         <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="N47" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O47" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -6869,7 +6866,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6898,10 +6895,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6924,17 +6921,17 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -6983,7 +6980,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7012,10 +7009,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7038,19 +7035,19 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7075,14 +7072,14 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
       </c>
@@ -7099,7 +7096,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7128,10 +7125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7154,19 +7151,19 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -7191,14 +7188,14 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
       </c>
@@ -7215,7 +7212,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7244,10 +7241,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7270,19 +7267,19 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -7307,14 +7304,14 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
       </c>
@@ -7331,7 +7328,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7360,10 +7357,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7386,17 +7383,17 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -7445,7 +7442,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7460,10 +7457,10 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>19</v>
@@ -7474,10 +7471,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7500,17 +7497,17 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -7559,7 +7556,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7588,10 +7585,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7614,17 +7611,17 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -7673,7 +7670,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7702,10 +7699,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7728,17 +7725,17 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -7787,7 +7784,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7816,10 +7813,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7842,17 +7839,17 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -7901,7 +7898,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7922,7 +7919,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -7930,10 +7927,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7956,13 +7953,13 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8013,43 +8010,43 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI57" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI57" t="s" s="2">
+      <c r="AJ57" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8071,13 +8068,13 @@
         <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="N58" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8127,7 +8124,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8151,19 +8148,19 @@
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8185,16 +8182,16 @@
         <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="N59" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8243,7 +8240,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8272,10 +8269,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8298,17 +8295,17 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -8333,14 +8330,14 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
       </c>
@@ -8357,7 +8354,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8386,10 +8383,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8412,17 +8409,17 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -8471,7 +8468,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
